--- a/important_mails_2026-04-07.xlsx
+++ b/important_mails_2026-04-07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,67 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
+          <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
+          <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Witamy!
+ Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
+ Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
+ Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
+ Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
+ Z poważaniem,
+ Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
+ Czy ten e-mail był pomocny?
+ SPC-EUAmazon-721281267923446</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -526,39 +572,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -570,39 +616,80 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions
+ 96
+ Starting May 5, 2026, we'll update the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, France, Italy and Spain stores.
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -623,39 +710,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -681,40 +768,40 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -731,39 +818,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -783,39 +870,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -832,94 +919,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon Services
- 96
- Review details about your EPR Pay on Behalf reserved amount
- Hello,
- Starting 01-04-2026, we'll hold €501.64 from your payments to cover the eco-contribution fees and Extended Producer Responsibility (EPR) Pay on Behalf service fees for sales of products subject to EPR obligations in our Amazon.es - Amazon.fr store in 2025.
- EPR Pay on Behalf calculates and pays eco-contribution fees for your sales, then debits those amounts from your account. Once fees are charged, any excess reserves will return to your account.
- Our records show you have products listed in the following EPR categories:
- - Do-it-yourself (DIY)
- - Electronical and electrical equipment
- - Packaging
- - Sports
- - Textile
- - Toys
- The amount held back is a combination of two fees:
- Due eco-contribution fees - €299.7
- EPR Pay on Behalf service fees - €201.94
- After 01-04-2026, to review your ASIN-level calculations, reserved amount details, and the reporting period for each EPR category, go to the EPR Pay on Behalf dashboard .
- The reserved amount will be adjusted monthly according to your sales volume. If the reserved amount isn't enough to cover the eco-contributions, we'll charge the additional </t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -942,39 +974,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -992,39 +1024,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1042,39 +1074,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -1094,39 +1126,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1138,39 +1170,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1182,39 +1214,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1226,39 +1258,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1270,39 +1302,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1314,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1358,39 +1390,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1402,39 +1434,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1453,39 +1485,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1497,39 +1529,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1541,39 +1573,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1585,39 +1617,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1629,39 +1661,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1673,39 +1705,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1717,39 +1749,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1761,39 +1793,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1812,39 +1844,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1856,40 +1888,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1908,39 +1940,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1952,39 +1984,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2003,39 +2035,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2067,39 +2099,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2126,39 +2158,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2170,39 +2202,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -2212,39 +2244,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -2254,39 +2286,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -2316,39 +2348,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -2366,39 +2398,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -2412,54 +2444,6 @@
 您的 ASIN 推荐清单
 以下是为您精选的推荐 ASIN，用于提交至科技周活动。
 &lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D95; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
-Dear there,
-Thank you again for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61cb1y/1376709412/h/1WNFlb9vThQHSQY7UXRXBztlSOEepEEyvW_3PEnZTWk
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-These updates support Amazon</t>
         </is>
       </c>
     </row>
@@ -3195,21 +3179,76 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
+          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ 96
+ Review details about your EPR Pay on Behalf reserved amount
+ Hello,
+ Starting 01-04-2026, we'll hold €501.64 from your payments to cover the eco-contribution fees and Extended Producer Responsibility (EPR) Pay on Behalf service fees for sales of products subject to EPR obligations in our Amazon.es - Amazon.fr store in 2025.
+ EPR Pay on Behalf calculates and pays eco-contribution fees for your sales, then debits those amounts from your account. Once fees are charged, any excess reserves will return to your account.
+ Our records show you have products listed in the following EPR categories:
+ - Do-it-yourself (DIY)
+ - Electronical and electrical equipment
+ - Packaging
+ - Sports
+ - Textile
+ - Toys
+ The amount held back is a combination of two fees:
+ Due eco-contribution fees - €299.7
+ EPR Pay on Behalf service fees - €201.94
+ After 01-04-2026, to review your ASIN-level calculations, reserved amount details, and the reporting period for each EPR category, go to the EPR Pay on Behalf dashboard .
+ The reserved amount will be adjusted monthly according to your sales volume. If the reserved amount isn't enough to cover the eco-contributions, we'll charge the additional </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3229,39 +3268,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3278,39 +3317,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3327,39 +3366,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -3374,39 +3413,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3430,39 +3469,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3476,59 +3515,10 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Negatieve saldoaanpassing voor al je accounts</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- We hebben je negatieve saldo van €11.99 dat verschuldigd was via je Amazon.nl verkopersaccount op maart 8, 2026, aangepast met geld dat beschikbaar was in je Amazon.it account. Je kunt je accountsaldo op elk gewenst moment bekijken door in te loggen op je account en naar het Betalingsdashboard te gaan.
-Ga voor meer informatie naar Negatieve saldoaanpassing voor al je accounts .
-Met vriendelijke groet,
-Amazon Payments Europe
- Rapporteer een probleem met deze e-mail
- Als je vragen hebt, ga dan naar: Seller Central
- Om je e-mailvoorkeuren te wijzigen, ga je naar: Voorkeuren voor meldingen
- Auteursrecht (copyright) 2026 Amazon, Inc. of haar dochterondernemingen. Alle rechten voorbehouden.
- Amazon Payments Europe S.C.A. (société en commandite par actions), een commanditaire vennootschap op aandelen, is een bedrijf dat is geregistreerd in Luxemburg onder registratienummer (RCS Luxembourg) B 153 265, met het hoofdkantoor op 38 Avenue J.F. Kennedy, L-1855 Luxemburg. Btw-nummer LU 24448288.
- Amazon Payments Europe S.C.A. is geautoriseerd door de Commission de Surveillance du Secteur Financier in Luxemburg en staat onder toezicht van de Central B</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3543,7 +3533,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
+          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3553,63 +3543,11 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
-On 03/08/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
- 108.10.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
- Amazon sellers and Amazon Pay merchants can si</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3627,39 +3565,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3677,39 +3615,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3727,39 +3665,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3774,39 +3712,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3824,39 +3762,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3874,39 +3812,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3924,39 +3862,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3971,39 +3909,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4018,39 +3956,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4065,39 +4003,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4116,40 +4054,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -4168,39 +4106,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4210,39 +4148,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4260,39 +4198,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4308,39 +4246,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4359,39 +4297,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4409,39 +4347,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4463,39 +4401,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4515,6 +4453,54 @@
 To contact us again about this issue, please use the Contact Us form in Seller Central using the following link:
 https://sellercentral.amazon.com/cu/case-dashboard/view-case?caseID=18425733131
 Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
+Dear there,
+Thank you again for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61cb1y/1376709412/h/1WNFlb9vThQHSQY7UXRXBztlSOEepEEyvW_3PEnZTWk
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+These updates support Amazon</t>
         </is>
       </c>
     </row>
@@ -6797,55 +6783,6 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>96
-Wijziging in geschiktheid voor opties voor premiumverzending
-Weihai EU,
-Je komt momenteel niet in aanmerking om Premium-verzendopties aan te bieden voor door verkoper afgehandelde bestellingen. Je status is gewijzigd omdat we hebben gemerkt dat een of meer van je prestatiestatistieken onder de programmavereisten zijn gedaald.
-Je kunt je prestatiestatistieken bekijken met behulp van de widget Geschiktheid voor Premium-verzending . Als je weer in aanmerking wilt komen voor Premium-verzendopties, moet je een actieplan indienen door op deze e-mail te reageren of te schrijven naar op-pso-vtr-appeals@amazon.nl .
-Om Premium-verzendopties aan te bieden, moeten verkopers het volgende doen:
-- 90 dagen of langer verkopen op Amazon
-- Tien of meer bestellingen in de laatste 30 dagen hebben verzonden
-- Een percentage tijdige bezorgingen van 97% of hoger behouden voor alle bestellingen met Premium-verzendopties
-- Een percentage geldige trackingnummers van 100% behouden voor alle bestellingen met Premium-verzendopties
-- Een annuleringspercentage van 0,5% of minder behouden voor alle bestellingen met Premium-verzendopties
-Verzonden door Amazon-bestellingen (FBA) worden niet beïnvloed door deze s</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/important_mails_2026-04-07.xlsx
+++ b/important_mails_2026-04-07.xlsx
@@ -1077,7 +1077,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1092,73 +1092,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
+          <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Address compliance requirements for your listings</t>
+          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-Action required: Important information about your product listings
- We are contacting you because you have listed products that require you to submit compliance documents.
- Product listings are missing required compliance documents
- Hello,
- We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
- Review Compliance Requirements
- The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
- SKU ASIN Listing Status WH-PW Kit0806 B0DSM44PRS Removed
- Why is this happening?
-This requirement helps to ensure that products are compliant with local laws and safe for customers.
- How do I continue to sell the affected products?
-Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
- Was there an error?
-If you believe that you do not need to su</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1170,39 +1118,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1214,39 +1162,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1258,39 +1206,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1302,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1346,39 +1294,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1390,39 +1338,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1434,39 +1382,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1485,39 +1433,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1529,39 +1477,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1573,39 +1521,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1617,39 +1565,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1661,39 +1609,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1705,39 +1653,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1749,39 +1697,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1793,39 +1741,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1844,39 +1792,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1888,40 +1836,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1940,39 +1888,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1984,39 +1932,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2035,39 +1983,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2099,39 +2047,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2158,39 +2106,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2202,39 +2150,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -2244,39 +2192,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -2286,39 +2234,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -2348,39 +2296,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -2398,39 +2346,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -2447,39 +2395,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2492,39 +2440,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2542,39 +2490,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -2604,39 +2552,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2656,40 +2604,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2705,39 +2653,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2757,39 +2705,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2815,39 +2763,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2863,39 +2811,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2916,39 +2864,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2962,40 +2910,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -3011,39 +2959,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3063,39 +3011,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -3109,39 +3057,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3161,39 +3109,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3216,39 +3164,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3268,39 +3216,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3317,39 +3265,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3366,39 +3314,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -3413,39 +3361,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3469,39 +3417,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3512,6 +3460,58 @@
  Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
  Czy ten e-mail był pomocny?
  SPC-EUAmazon-1037940607738415</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Address compliance requirements for your listings</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>96
+Action required: Important information about your product listings
+ We are contacting you because you have listed products that require you to submit compliance documents.
+ Product listings are missing required compliance documents
+ Hello,
+ We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
+ Review Compliance Requirements
+ The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
+ SKU ASIN Listing Status WH-PW Kit0806 B0DSM44PRS Removed
+ Why is this happening?
+This requirement helps to ensure that products are compliant with local laws and safe for customers.
+ How do I continue to sell the affected products?
+Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
+ Was there an error?
+If you believe that you do not need to su</t>
         </is>
       </c>
     </row>
